--- a/design/技能表.xlsx
+++ b/design/技能表.xlsx
@@ -760,7 +760,7 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">

--- a/design/技能表.xlsx
+++ b/design/技能表.xlsx
@@ -1,32 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\聚光灯\Hunter\design\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <ns1:AlternateContent>
+    <ns1:Choice Requires="x15">
+      <ns2:absPath url="E:\聚光灯\Hunter\design\"/>
+    </ns1:Choice>
+  </ns1:AlternateContent>
   <bookViews>
     <workbookView windowWidth="24750" windowHeight="12060" firstSheet="1"/>
   </bookViews>
   <sheets>
     <sheet name="技能|Skill" sheetId="1" r:id="rId1"/>
     <sheet name="属性|Attribute" sheetId="2" r:id="rId2"/>
+    <sheet name="技能效果|SkillEffect" sheetId="3" r:id="rIdCfg3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <ns4:calcFeatures>
+        <ns4:feature name="microsoft.com:RD"/>
+        <ns4:feature name="microsoft.com:Single"/>
+        <ns4:feature name="microsoft.com:FV"/>
+        <ns4:feature name="microsoft.com:CNMTM"/>
+        <ns4:feature name="microsoft.com:LET_WF"/>
+        <ns4:feature name="microsoft.com:LAMBDA_WF"/>
+        <ns4:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </ns4:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -426,14 +427,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" ns1:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -650,8 +651,36 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF17344A"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF17344A"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="44">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -874,8 +903,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8CDE1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8CDE1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="29">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1249,8 +1300,10 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
+    <border/>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1399,8 +1452,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="38" borderId="29"/>
+    <xf numFmtId="0" fontId="34" fillId="41" borderId="30"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1494,6 +1549,62 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="38" borderId="29" xfId="50"/>
+    <xf numFmtId="0" fontId="31" fillId="40" borderId="29" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="40" borderId="29" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="40" borderId="29" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="40" borderId="29" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="40" borderId="29" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="38" borderId="29" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="40" borderId="29" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="40" borderId="29" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="38" borderId="29" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="38" borderId="29" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="40" borderId="29" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="41" borderId="30" xfId="51"/>
+    <xf numFmtId="0" fontId="34" fillId="43" borderId="30" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="43" borderId="30" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="43" borderId="30" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="43" borderId="30" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="43" borderId="30" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="41" borderId="30" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="43" borderId="30" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="43" borderId="30" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="41" borderId="30" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="41" borderId="30" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="43" borderId="30" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1741,7 +1852,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" ns2:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1750,7 +1861,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" ns2:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1769,8 +1880,8 @@
     </mruColors>
   </colors>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1968,21 +2079,169 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/cfg3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="47" t="str">
+        <v>效果ID</v>
+      </c>
+      <c r="B1" s="47" t="str">
+        <v>技能ID</v>
+      </c>
+      <c r="C1" s="47" t="str">
+        <v>属性代码</v>
+      </c>
+      <c r="D1" s="47" t="str">
+        <v>运算 add/mul_bp</v>
+      </c>
+      <c r="E1" s="47" t="str">
+        <v>固定量或基点因子</v>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="47" t="str">
+        <v>int32</v>
+      </c>
+      <c r="B2" s="47" t="str">
+        <v>int32</v>
+      </c>
+      <c r="C2" s="47" t="str">
+        <v>string</v>
+      </c>
+      <c r="D2" s="47" t="str">
+        <v>string</v>
+      </c>
+      <c r="E2" s="47" t="str">
+        <v>int32</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="47" t="str">
+        <v>EffectIdx</v>
+      </c>
+      <c r="B3" s="47" t="str">
+        <v>SkillIdx</v>
+      </c>
+      <c r="C3" s="47" t="str">
+        <v>Stat</v>
+      </c>
+      <c r="D3" s="47" t="str">
+        <v>Op</v>
+      </c>
+      <c r="E3" s="47" t="str">
+        <v>Value</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="47" t="str">
+        <v>server/client/key</v>
+      </c>
+      <c r="B4" s="47" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="C4" s="47" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="D4" s="47" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="E4" s="47" t="str">
+        <v>server/client</v>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="48"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="48"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="48"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="48"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="48"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="48"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="48"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="48"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF577A9A"/>
   </sheetPr>
-  <dimension ref="A1:M503"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="20" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="42" style="1" customWidth="1"/>
-    <col min="4" max="5" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18" style="1" customWidth="1"/>
     <col min="6" max="6" width="17" style="1" customWidth="1"/>
-    <col min="7" max="11" width="24" style="1" customWidth="1"/>
-    <col min="13" max="13" width="55" customWidth="1"/>
+    <col min="7" max="7" width="24" style="1" customWidth="1"/>
+    <col min="8" max="8" width="24" style="1" customWidth="1"/>
+    <col min="9" max="9" width="24" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24" style="1" customWidth="1"/>
+    <col min="11" max="11" width="24" style="1" customWidth="1"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="70" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1" spans="1:13">
@@ -2004,8 +2263,8 @@
       <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="16" t="s">
-        <v>6</v>
+      <c r="G1" s="62" t="str">
+        <v>效果说明（仅展示）</v>
       </c>
       <c r="H1" s="16" t="s">
         <v>7</v>
@@ -2019,9 +2278,17 @@
       <c r="K1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="17"/>
-      <c r="M1" s="18" t="s">
-        <v>11</v>
+      <c r="L1" s="62" t="str">
+        <v>作用对象</v>
+      </c>
+      <c r="M1" s="62" t="str">
+        <v>效果类别</v>
+      </c>
+      <c r="N1" s="62" t="str">
+        <v>生命周期</v>
+      </c>
+      <c r="P1" s="60" t="str">
+        <v>v5 天赋规则</v>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:13">
@@ -2043,8 +2310,8 @@
       <c r="F2" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="19" t="s">
-        <v>13</v>
+      <c r="G2" s="62" t="str">
+        <v>string</v>
       </c>
       <c r="H2" s="19" t="s">
         <v>13</v>
@@ -2058,9 +2325,17 @@
       <c r="K2" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="20"/>
-      <c r="M2" s="21" t="s">
-        <v>14</v>
+      <c r="L2" s="62" t="str">
+        <v>string</v>
+      </c>
+      <c r="M2" s="62" t="str">
+        <v>string</v>
+      </c>
+      <c r="N2" s="62" t="str">
+        <v>string</v>
+      </c>
+      <c r="P2" s="60" t="str">
+        <v>效果在技能效果表逐项填写；缺值禁止选入生产。</v>
       </c>
     </row>
     <row r="3" ht="29" customHeight="1" spans="1:13">
@@ -2082,7 +2357,9 @@
       <c r="F3" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="19"/>
+      <c r="G3" s="62" t="str">
+        <v>EffectDesc</v>
+      </c>
       <c r="H3" s="19" t="s">
         <v>21</v>
       </c>
@@ -2095,8 +2372,16 @@
       <c r="K3" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="22"/>
-      <c r="M3" s="23"/>
+      <c r="L3" s="62" t="str">
+        <v>Target</v>
+      </c>
+      <c r="M3" s="62" t="str">
+        <v>Category</v>
+      </c>
+      <c r="N3" s="62" t="str">
+        <v>Lifetime</v>
+      </c>
+      <c r="P3" s="60" t="str"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:13">
       <c r="A4" s="19" t="s">
@@ -2117,7 +2402,9 @@
       <c r="F4" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="19"/>
+      <c r="G4" s="62" t="str">
+        <v>client</v>
+      </c>
       <c r="H4" s="19" t="s">
         <v>27</v>
       </c>
@@ -2130,8 +2417,16 @@
       <c r="K4" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="L4" s="22"/>
-      <c r="M4" s="23"/>
+      <c r="L4" s="62" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="M4" s="62" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="N4" s="62" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="P4" t="str"/>
     </row>
     <row r="5" s="15" customFormat="1" spans="1:13">
       <c r="A5" s="24">
@@ -2161,9 +2456,17 @@
       <c r="K5" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="L5" s="26"/>
-      <c r="M5" s="27" t="s">
-        <v>31</v>
+      <c r="L5" s="63" t="str">
+        <v>player</v>
+      </c>
+      <c r="M5" s="63" t="str">
+        <v>mechanic</v>
+      </c>
+      <c r="N5" s="63" t="str">
+        <v>once</v>
+      </c>
+      <c r="P5" t="str">
+        <v>技能10的轮转按射击间隔 shot_ticks 解释。</v>
       </c>
     </row>
     <row r="6" s="15" customFormat="1" spans="1:13">
@@ -2194,8 +2497,15 @@
       <c r="K6" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="L6" s="26"/>
-      <c r="M6" s="28"/>
+      <c r="L6" s="63" t="str">
+        <v>player</v>
+      </c>
+      <c r="M6" s="63" t="str">
+        <v>mechanic</v>
+      </c>
+      <c r="N6" s="63" t="str">
+        <v>death</v>
+      </c>
     </row>
     <row r="7" s="15" customFormat="1" spans="1:13">
       <c r="A7" s="24">
@@ -2225,8 +2535,18 @@
       <c r="K7" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="L7" s="26"/>
-      <c r="M7" s="28"/>
+      <c r="L7" s="63" t="str">
+        <v>player</v>
+      </c>
+      <c r="M7" s="63" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="N7" s="63" t="str">
+        <v>passive</v>
+      </c>
+      <c r="P7" s="18" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="8" s="15" customFormat="1" spans="1:13">
       <c r="A8" s="24">
@@ -2256,8 +2576,18 @@
       <c r="K8" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="L8" s="26"/>
-      <c r="M8" s="28"/>
+      <c r="L8" s="63" t="str">
+        <v>player</v>
+      </c>
+      <c r="M8" s="63" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="N8" s="63" t="str">
+        <v>passive</v>
+      </c>
+      <c r="P8" s="21" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="9" s="15" customFormat="1" spans="1:13">
       <c r="A9" s="24">
@@ -2287,8 +2617,18 @@
       <c r="K9" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="L9" s="26"/>
-      <c r="M9" s="28"/>
+      <c r="L9" s="63" t="str">
+        <v>player</v>
+      </c>
+      <c r="M9" s="63" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="N9" s="63" t="str">
+        <v>passive</v>
+      </c>
+      <c r="P9" s="27" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="10" s="15" customFormat="1" spans="1:13">
       <c r="A10" s="24">
@@ -2312,8 +2652,15 @@
       <c r="I10" s="25"/>
       <c r="J10" s="25"/>
       <c r="K10" s="25"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="28"/>
+      <c r="L10" s="63" t="str">
+        <v>player</v>
+      </c>
+      <c r="M10" s="63" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="N10" s="63" t="str">
+        <v>passive</v>
+      </c>
     </row>
     <row r="11" s="15" customFormat="1" spans="1:13">
       <c r="A11" s="24">
@@ -2337,8 +2684,15 @@
       <c r="I11" s="25"/>
       <c r="J11" s="25"/>
       <c r="K11" s="25"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="28"/>
+      <c r="L11" s="63" t="str">
+        <v>weapon</v>
+      </c>
+      <c r="M11" s="63" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="N11" s="63" t="str">
+        <v>passive</v>
+      </c>
     </row>
     <row r="12" s="15" customFormat="1" spans="1:13">
       <c r="A12" s="24">
@@ -2362,8 +2716,15 @@
       <c r="I12" s="25"/>
       <c r="J12" s="25"/>
       <c r="K12" s="25"/>
-      <c r="L12" s="26"/>
-      <c r="M12" s="28"/>
+      <c r="L12" s="63" t="str">
+        <v>weapon</v>
+      </c>
+      <c r="M12" s="63" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="N12" s="63" t="str">
+        <v>passive</v>
+      </c>
     </row>
     <row r="13" s="15" customFormat="1" spans="1:13">
       <c r="A13" s="24">
@@ -2393,8 +2754,16 @@
       <c r="K13" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="L13" s="26"/>
-      <c r="M13" s="27" t="s">
+      <c r="L13" s="63" t="str">
+        <v>weapon</v>
+      </c>
+      <c r="M13" s="63" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="N13" s="63" t="str">
+        <v>passive</v>
+      </c>
+      <c r="P13" s="27" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2426,8 +2795,15 @@
       <c r="K14" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="L14" s="26"/>
-      <c r="M14" s="28"/>
+      <c r="L14" s="63" t="str">
+        <v>weapon</v>
+      </c>
+      <c r="M14" s="63" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="N14" s="63" t="str">
+        <v>passive</v>
+      </c>
     </row>
     <row r="15" s="15" customFormat="1" spans="1:13">
       <c r="A15" s="24">
@@ -2457,8 +2833,15 @@
       <c r="K15" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="L15" s="26"/>
-      <c r="M15" s="28"/>
+      <c r="L15" s="63" t="str">
+        <v>tool</v>
+      </c>
+      <c r="M15" s="63" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="N15" s="63" t="str">
+        <v>passive</v>
+      </c>
     </row>
     <row r="16" s="15" customFormat="1" spans="1:13">
       <c r="A16" s="24">
@@ -2488,8 +2871,15 @@
       <c r="K16" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="L16" s="26"/>
-      <c r="M16" s="28"/>
+      <c r="L16" s="63" t="str">
+        <v>tool</v>
+      </c>
+      <c r="M16" s="63" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="N16" s="63" t="str">
+        <v>passive</v>
+      </c>
     </row>
     <row r="17" s="15" customFormat="1" spans="1:13">
       <c r="A17" s="24">
@@ -2519,8 +2909,15 @@
       <c r="K17" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="L17" s="26"/>
-      <c r="M17" s="28"/>
+      <c r="L17" s="63" t="str">
+        <v>tool</v>
+      </c>
+      <c r="M17" s="63" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="N17" s="63" t="str">
+        <v>passive</v>
+      </c>
     </row>
     <row r="18" s="15" customFormat="1" spans="1:13">
       <c r="A18" s="24">
@@ -2544,8 +2941,15 @@
       <c r="I18" s="25"/>
       <c r="J18" s="25"/>
       <c r="K18" s="25"/>
-      <c r="L18" s="26"/>
-      <c r="M18" s="28"/>
+      <c r="L18" s="63" t="str">
+        <v>tool</v>
+      </c>
+      <c r="M18" s="63" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="N18" s="63" t="str">
+        <v>passive</v>
+      </c>
     </row>
     <row r="19" s="15" customFormat="1" ht="17.25" spans="1:13">
       <c r="A19" s="24">
@@ -2569,8 +2973,15 @@
       <c r="I19" s="25"/>
       <c r="J19" s="25"/>
       <c r="K19" s="25"/>
-      <c r="L19" s="29"/>
-      <c r="M19" s="30"/>
+      <c r="L19" s="63" t="str">
+        <v>tool</v>
+      </c>
+      <c r="M19" s="63" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="N19" s="63" t="str">
+        <v>passive</v>
+      </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="13"/>

--- a/design/技能表.xlsx
+++ b/design/技能表.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能|Skill" sheetId="1" r:id="R504964106bbb4995"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性|Attribute" sheetId="2" r:id="R6663542bfd98427f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技能效果|SkillEffect" sheetId="3" r:id="R12b032a444a840b6"/>
-  </x:sheets>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheets>
+    <sheet name="技能|Skill" sheetId="1" r:id="R504964106bbb4995"/>
+    <sheet name="属性|Attribute" sheetId="2" r:id="R6663542bfd98427f"/>
+    <sheet name="技能效果|SkillEffect" sheetId="3" r:id="R12b032a444a840b6"/>
+  </sheets>
+</workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -69,259 +69,259 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
-    <x:numFmt numFmtId="200" formatCode="0"/>
-    <x:numFmt numFmtId="201" formatCode="@"/>
-  </x:numFmts>
-  <x:fonts count="7">
-    <x:font>
-      <x:sz val="11"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF243746"/>
-      <x:name val="Microsoft YaHei UI"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FF193348"/>
-      <x:name val="Microsoft YaHei UI"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF795A33"/>
-      <x:name val="Microsoft YaHei UI"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FF795A33"/>
-      <x:name val="Microsoft YaHei UI"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF243746"/>
-      <x:name val="Microsoft YaHei"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FF193348"/>
-      <x:name val="Microsoft YaHei"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="7">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFB9CEE3"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFFFF"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF3F6FA"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFF1D0"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFB8CDE1"/>
-      </x:patternFill>
-    </x:fill>
-  </x:fills>
-  <x:borders count="3">
-    <x:border/>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFFFFFFF"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFFFFFFF"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFFFFFFF"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFFFFFFF"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:bottom style="thin">
-        <x:color rgb="FFDCE4EC"/>
-      </x:bottom>
-    </x:border>
-  </x:borders>
-  <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </x:cellStyleXfs>
-  <x:cellXfs count="47">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0"/>
-  </x:cellStyles>
-  <x:dxfs count="1">
-    <x:dxf>
-      <x:font>
-        <x:color rgb="FF7A5627"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFFF4DF"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-  </x:dxfs>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="200" formatCode="0"/>
+    <numFmt numFmtId="201" formatCode="@"/>
+  </numFmts>
+  <fonts count="7">
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF243746"/>
+      <name val="Microsoft YaHei UI"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF193348"/>
+      <name val="Microsoft YaHei UI"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF795A33"/>
+      <name val="Microsoft YaHei UI"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF795A33"/>
+      <name val="Microsoft YaHei UI"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF243746"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF193348"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+  </fonts>
+  <fills count="7">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9CEE3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF1D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8CDE1"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="3">
+    <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="FFDCE4EC"/>
+      </bottom>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="47">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="201" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="201" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="201" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0"/>
+  </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF7A5627"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF4DF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -516,751 +516,751 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="21" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="21" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="21" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="64" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="24" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="24" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="115" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="7" t="str">
-        <x:v>技能ID</x:v>
-      </x:c>
-      <x:c r="B1" s="7" t="str">
-        <x:v>技能名称</x:v>
-      </x:c>
-      <x:c r="C1" s="7" t="str">
-        <x:v>技能说明</x:v>
-      </x:c>
-      <x:c r="D1" s="7" t="str">
-        <x:v>消耗技能点</x:v>
-      </x:c>
-      <x:c r="E1" s="7" t="str">
-        <x:v>作用对象</x:v>
-      </x:c>
-      <x:c r="F1" s="7" t="str">
-        <x:v>效果类别</x:v>
-      </x:c>
-      <x:c r="G1" s="7" t="str">
-        <x:v>生命周期</x:v>
-      </x:c>
-      <x:c r="H1" s="7" t="str">
-        <x:v>效果展示说明</x:v>
-      </x:c>
-      <x:c r="I1" s="7" t="str">
-        <x:v>技能图标</x:v>
-      </x:c>
-      <x:c r="J1" s="7" t="str">
-        <x:v>动画资源</x:v>
-      </x:c>
-      <x:c r="K1" s="7" t="str">
-        <x:v>特效资源</x:v>
-      </x:c>
-      <x:c r="L1" s="7" t="str">
-        <x:v>音效资源</x:v>
-      </x:c>
-      <x:c r="M1" s="7" t="str">
-        <x:v>是否启用</x:v>
-      </x:c>
-      <x:c r="O1" s="28" t="str">
-        <x:v>技能配置说明</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="32" customHeight="1">
-      <x:c r="A2" s="7" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="B2" s="7" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="C2" s="7" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="D2" s="7" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E2" s="7" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="F2" s="7" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="G2" s="7" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="H2" s="7" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="I2" s="7" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="J2" s="7" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="K2" s="7" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="L2" s="7" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="M2" s="7" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="O2" s="26" t="str">
-        <x:v>来源：技能表完整配置方案.md（2026-10-03）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="32" customHeight="1">
-      <x:c r="A3" s="7" t="str">
-        <x:v>SkillIdx</x:v>
-      </x:c>
-      <x:c r="B3" s="7" t="str">
-        <x:v>Name</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="str">
-        <x:v>Desc</x:v>
-      </x:c>
-      <x:c r="D3" s="7" t="str">
-        <x:v>Cost</x:v>
-      </x:c>
-      <x:c r="E3" s="7" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="F3" s="7" t="str">
-        <x:v>Category</x:v>
-      </x:c>
-      <x:c r="G3" s="7" t="str">
-        <x:v>Lifetime</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="str">
-        <x:v>EffectDesc</x:v>
-      </x:c>
-      <x:c r="I3" s="7" t="str">
-        <x:v>IconId</x:v>
-      </x:c>
-      <x:c r="J3" s="7" t="str">
-        <x:v>AnimId</x:v>
-      </x:c>
-      <x:c r="K3" s="7" t="str">
-        <x:v>EffectId</x:v>
-      </x:c>
-      <x:c r="L3" s="7" t="str">
-        <x:v>SoundId</x:v>
-      </x:c>
-      <x:c r="M3" s="7" t="str">
-        <x:v>Enabled</x:v>
-      </x:c>
-      <x:c r="O3" s="26"/>
-    </x:row>
-    <x:row r="4" ht="32" customHeight="1">
-      <x:c r="A4" s="7" t="str">
-        <x:v>server/client/key</x:v>
-      </x:c>
-      <x:c r="B4" s="7" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="C4" s="7" t="str">
-        <x:v>client</x:v>
-      </x:c>
-      <x:c r="D4" s="7" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="E4" s="7" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="F4" s="7" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="G4" s="7" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="H4" s="7" t="str">
-        <x:v>client</x:v>
-      </x:c>
-      <x:c r="I4" s="7" t="str">
-        <x:v>client</x:v>
-      </x:c>
-      <x:c r="J4" s="7" t="str">
-        <x:v>client</x:v>
-      </x:c>
-      <x:c r="K4" s="7" t="str">
-        <x:v>client</x:v>
-      </x:c>
-      <x:c r="L4" s="7" t="str">
-        <x:v>client</x:v>
-      </x:c>
-      <x:c r="M4" s="7" t="str">
-        <x:v>server/client</x:v>
-      </x:c>
-      <x:c r="O4" s="26"/>
-    </x:row>
-    <x:row r="5" ht="46" customHeight="1">
-      <x:c r="A5" s="13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B5" s="14" t="str">
-        <x:v>死灵法师</x:v>
-      </x:c>
-      <x:c r="C5" s="21" t="str">
-        <x:v>可在对局中复活一次</x:v>
-      </x:c>
-      <x:c r="D5" s="13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E5" s="14" t="str">
-        <x:v>player</x:v>
-      </x:c>
-      <x:c r="F5" s="14" t="str">
-        <x:v>mechanic</x:v>
-      </x:c>
-      <x:c r="G5" s="14" t="str">
-        <x:v>once</x:v>
-      </x:c>
-      <x:c r="H5" s="21" t="str">
-        <x:v>成功复活恢复25点生命和40点体力，本局只能使用一次</x:v>
-      </x:c>
-      <x:c r="I5" s="14"/>
-      <x:c r="J5" s="14"/>
-      <x:c r="K5" s="14"/>
-      <x:c r="L5" s="14"/>
-      <x:c r="M5" s="13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="26" t="str">
-        <x:v>15项技能完整保留，技能ID和技能点成本不变。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="46" customHeight="1">
-      <x:c r="A6" s="17" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B6" s="18" t="str">
-        <x:v>重振旗鼓</x:v>
-      </x:c>
-      <x:c r="C6" s="22" t="str">
-        <x:v>复活后将血量恢复至上限</x:v>
-      </x:c>
-      <x:c r="D6" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E6" s="18" t="str">
-        <x:v>player</x:v>
-      </x:c>
-      <x:c r="F6" s="18" t="str">
-        <x:v>mechanic</x:v>
-      </x:c>
-      <x:c r="G6" s="18" t="str">
-        <x:v>death</x:v>
-      </x:c>
-      <x:c r="H6" s="22" t="str">
-        <x:v>成功复活时恢复至最大生命，复活后移除本技能</x:v>
-      </x:c>
-      <x:c r="I6" s="18"/>
-      <x:c r="J6" s="18"/>
-      <x:c r="K6" s="18"/>
-      <x:c r="L6" s="18"/>
-      <x:c r="M6" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="26" t="str">
-        <x:v>技能3、6、14、15尚待扩展，Enabled=0；其余11项按方案填1。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="46" customHeight="1">
-      <x:c r="A7" s="13" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B7" s="14" t="str">
-        <x:v>精力充沛</x:v>
-      </x:c>
-      <x:c r="C7" s="21" t="str">
-        <x:v>降低奔跑时体力消耗</x:v>
-      </x:c>
-      <x:c r="D7" s="13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E7" s="14" t="str">
-        <x:v>player</x:v>
-      </x:c>
-      <x:c r="F7" s="14" t="str">
-        <x:v>numeric</x:v>
-      </x:c>
-      <x:c r="G7" s="14" t="str">
-        <x:v>passive</x:v>
-      </x:c>
-      <x:c r="H7" s="21" t="str">
-        <x:v>奔跑体力消耗降低30%</x:v>
-      </x:c>
-      <x:c r="I7" s="14"/>
-      <x:c r="J7" s="14"/>
-      <x:c r="K7" s="14"/>
-      <x:c r="L7" s="14"/>
-      <x:c r="M7" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O7" s="26" t="str">
-        <x:v>全部数值按方案初值填写。1表示候选调试启用，仍须通过运行能力校验。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="46" customHeight="1">
-      <x:c r="A8" s="17" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B8" s="18" t="str">
-        <x:v>军需官</x:v>
-      </x:c>
-      <x:c r="C8" s="22" t="str">
-        <x:v>提升角色负重能力</x:v>
-      </x:c>
-      <x:c r="D8" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E8" s="18" t="str">
-        <x:v>player</x:v>
-      </x:c>
-      <x:c r="F8" s="18" t="str">
-        <x:v>numeric</x:v>
-      </x:c>
-      <x:c r="G8" s="18" t="str">
-        <x:v>passive</x:v>
-      </x:c>
-      <x:c r="H8" s="22" t="str">
-        <x:v>枪械配装负重上限增加1点</x:v>
-      </x:c>
-      <x:c r="I8" s="18"/>
-      <x:c r="J8" s="18"/>
-      <x:c r="K8" s="18"/>
-      <x:c r="L8" s="18"/>
-      <x:c r="M8" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="26" t="str">
-        <x:v>图标、动画、特效、音效尚无真实资源ID，空值表示未提供。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="46" customHeight="1">
-      <x:c r="A9" s="13" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B9" s="14" t="str">
-        <x:v>灵缇</x:v>
-      </x:c>
-      <x:c r="C9" s="21" t="str">
-        <x:v>提升一定奔跑速度</x:v>
-      </x:c>
-      <x:c r="D9" s="13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="str">
-        <x:v>player</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="str">
-        <x:v>numeric</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="str">
-        <x:v>passive</x:v>
-      </x:c>
-      <x:c r="H9" s="21" t="str">
-        <x:v>奔跑速度增加20%</x:v>
-      </x:c>
-      <x:c r="I9" s="14"/>
-      <x:c r="J9" s="14"/>
-      <x:c r="K9" s="14"/>
-      <x:c r="L9" s="14"/>
-      <x:c r="M9" s="13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="26" t="str">
-        <x:v>新AttributeId外键和Enabled开关仍需配置解析接入。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="46" customHeight="1">
-      <x:c r="A10" s="17" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B10" s="18" t="str">
-        <x:v>猫步</x:v>
-      </x:c>
-      <x:c r="C10" s="22" t="str">
-        <x:v>降低角色行动时发出的声音</x:v>
-      </x:c>
-      <x:c r="D10" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E10" s="18" t="str">
-        <x:v>player</x:v>
-      </x:c>
-      <x:c r="F10" s="18" t="str">
-        <x:v>numeric</x:v>
-      </x:c>
-      <x:c r="G10" s="18" t="str">
-        <x:v>passive</x:v>
-      </x:c>
-      <x:c r="H10" s="22" t="str">
-        <x:v>地面行走、奔跑和匍匐的行动声传播半径降低50%</x:v>
-      </x:c>
-      <x:c r="I10" s="18"/>
-      <x:c r="J10" s="18"/>
-      <x:c r="K10" s="18"/>
-      <x:c r="L10" s="18"/>
-      <x:c r="M10" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O10" s="26" t="str">
-        <x:v>货运骡子增加每种适用工具的携带次数上限，不自动补发数量或库存。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="46" customHeight="1">
-      <x:c r="A11" s="13" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B11" s="14" t="str">
-        <x:v>枪斗术</x:v>
-      </x:c>
-      <x:c r="C11" s="21" t="str">
-        <x:v>增加枪械近战伤害</x:v>
-      </x:c>
-      <x:c r="D11" s="13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="str">
-        <x:v>weapon</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="str">
-        <x:v>numeric</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="str">
-        <x:v>passive</x:v>
-      </x:c>
-      <x:c r="H11" s="21" t="str">
-        <x:v>枪械近战伤害增加50%</x:v>
-      </x:c>
-      <x:c r="I11" s="14"/>
-      <x:c r="J11" s="14"/>
-      <x:c r="K11" s="14"/>
-      <x:c r="L11" s="14"/>
-      <x:c r="M11" s="13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O11" s="26" t="str">
-        <x:v>技能10按枪械射击间隔shot_ticks配置，不修改瞄准精度或切枪速度。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="46" customHeight="1">
-      <x:c r="A12" s="17" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B12" s="18" t="str">
-        <x:v>弹药大师</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="str">
-        <x:v>提升枪械初始备弹</x:v>
-      </x:c>
-      <x:c r="D12" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E12" s="18" t="str">
-        <x:v>weapon</x:v>
-      </x:c>
-      <x:c r="F12" s="18" t="str">
-        <x:v>numeric</x:v>
-      </x:c>
-      <x:c r="G12" s="18" t="str">
-        <x:v>passive</x:v>
-      </x:c>
-      <x:c r="H12" s="22" t="str">
-        <x:v>开局时枪械初始备弹翻倍，不增加弹匣容量</x:v>
-      </x:c>
-      <x:c r="I12" s="18"/>
-      <x:c r="J12" s="18"/>
-      <x:c r="K12" s="18"/>
-      <x:c r="L12" s="18"/>
-      <x:c r="M12" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O12" s="26" t="str">
-        <x:v>once/death均在成功复活提交时消费，失败请求不消费。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="46" customHeight="1">
-      <x:c r="A13" s="13" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B13" s="14" t="str">
-        <x:v>手速超群</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="str">
-        <x:v>减少换弹时间</x:v>
-      </x:c>
-      <x:c r="D13" s="13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="str">
-        <x:v>weapon</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="str">
-        <x:v>numeric</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="str">
-        <x:v>passive</x:v>
-      </x:c>
-      <x:c r="H13" s="21" t="str">
-        <x:v>枪械每轮装填时间减少25%</x:v>
-      </x:c>
-      <x:c r="I13" s="14"/>
-      <x:c r="J13" s="14"/>
-      <x:c r="K13" s="14"/>
-      <x:c r="L13" s="14"/>
-      <x:c r="M13" s="13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="26" t="str">
-        <x:v>技能效果在技能效果表逐项维护，EffectDesc仅用于展示。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="46" customHeight="1">
-      <x:c r="A14" s="17" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B14" s="18" t="str">
-        <x:v>稳定瞄准</x:v>
-      </x:c>
-      <x:c r="C14" s="22" t="str">
-        <x:v>减少武器轮转时间，本版指射击间隔</x:v>
-      </x:c>
-      <x:c r="D14" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E14" s="18" t="str">
-        <x:v>weapon</x:v>
-      </x:c>
-      <x:c r="F14" s="18" t="str">
-        <x:v>numeric</x:v>
-      </x:c>
-      <x:c r="G14" s="18" t="str">
-        <x:v>passive</x:v>
-      </x:c>
-      <x:c r="H14" s="22" t="str">
-        <x:v>枪械射击间隔减少20%</x:v>
-      </x:c>
-      <x:c r="I14" s="18"/>
-      <x:c r="J14" s="18"/>
-      <x:c r="K14" s="18"/>
-      <x:c r="L14" s="18"/>
-      <x:c r="M14" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="46" customHeight="1">
-      <x:c r="A15" s="13" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B15" s="14" t="str">
-        <x:v>妙手回春</x:v>
-      </x:c>
-      <x:c r="C15" s="21" t="str">
-        <x:v>医疗包的使用时长减半</x:v>
-      </x:c>
-      <x:c r="D15" s="13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="str">
-        <x:v>tool</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="str">
-        <x:v>numeric</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="str">
-        <x:v>passive</x:v>
-      </x:c>
-      <x:c r="H15" s="21" t="str">
-        <x:v>医疗包使用时长减少50%</x:v>
-      </x:c>
-      <x:c r="I15" s="14"/>
-      <x:c r="J15" s="14"/>
-      <x:c r="K15" s="14"/>
-      <x:c r="L15" s="14"/>
-      <x:c r="M15" s="13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="46" customHeight="1">
-      <x:c r="A16" s="17" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B16" s="18" t="str">
-        <x:v>灵丹妙药</x:v>
-      </x:c>
-      <x:c r="C16" s="22" t="str">
-        <x:v>医疗包的治疗效果翻倍</x:v>
-      </x:c>
-      <x:c r="D16" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E16" s="18" t="str">
-        <x:v>tool</x:v>
-      </x:c>
-      <x:c r="F16" s="18" t="str">
-        <x:v>numeric</x:v>
-      </x:c>
-      <x:c r="G16" s="18" t="str">
-        <x:v>passive</x:v>
-      </x:c>
-      <x:c r="H16" s="22" t="str">
-        <x:v>医疗包治疗量翻倍，实际生命不超过最大生命</x:v>
-      </x:c>
-      <x:c r="I16" s="18"/>
-      <x:c r="J16" s="18"/>
-      <x:c r="K16" s="18"/>
-      <x:c r="L16" s="18"/>
-      <x:c r="M16" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="46" customHeight="1">
-      <x:c r="A17" s="13" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B17" s="14" t="str">
-        <x:v>投球好手</x:v>
-      </x:c>
-      <x:c r="C17" s="21" t="str">
-        <x:v>增加投掷物投掷距离</x:v>
-      </x:c>
-      <x:c r="D17" s="13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="str">
-        <x:v>tool</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="str">
-        <x:v>numeric</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="str">
-        <x:v>passive</x:v>
-      </x:c>
-      <x:c r="H17" s="21" t="str">
-        <x:v>当前已实现的炸药最大投掷距离增加50%</x:v>
-      </x:c>
-      <x:c r="I17" s="14"/>
-      <x:c r="J17" s="14"/>
-      <x:c r="K17" s="14"/>
-      <x:c r="L17" s="14"/>
-      <x:c r="M17" s="13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="46" customHeight="1">
-      <x:c r="A18" s="17" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B18" s="18" t="str">
-        <x:v>开箱大师</x:v>
-      </x:c>
-      <x:c r="C18" s="22" t="str">
-        <x:v>互动道具箱时可以额外获得一个道具</x:v>
-      </x:c>
-      <x:c r="D18" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E18" s="18" t="str">
-        <x:v>player</x:v>
-      </x:c>
-      <x:c r="F18" s="18" t="str">
-        <x:v>mechanic</x:v>
-      </x:c>
-      <x:c r="G18" s="18" t="str">
-        <x:v>passive</x:v>
-      </x:c>
-      <x:c r="H18" s="22" t="str">
-        <x:v>成功打开适用道具箱时，额外取得同一箱子奖励来源中的1个道具</x:v>
-      </x:c>
-      <x:c r="I18" s="18"/>
-      <x:c r="J18" s="18"/>
-      <x:c r="K18" s="18"/>
-      <x:c r="L18" s="18"/>
-      <x:c r="M18" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="46" customHeight="1">
-      <x:c r="A19" s="13" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B19" s="14" t="str">
-        <x:v>货运骡子</x:v>
-      </x:c>
-      <x:c r="C19" s="21" t="str">
-        <x:v>非消耗品道具额外增加携带量</x:v>
-      </x:c>
-      <x:c r="D19" s="13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="str">
-        <x:v>tool</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="str">
-        <x:v>numeric</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="str">
-        <x:v>passive</x:v>
-      </x:c>
-      <x:c r="H19" s="21" t="str">
-        <x:v>每种适用非消耗品工具的携带次数上限增加1，不自动补发数量</x:v>
-      </x:c>
-      <x:c r="I19" s="14"/>
-      <x:c r="J19" s="14"/>
-      <x:c r="K19" s="14"/>
-      <x:c r="L19" s="14"/>
-      <x:c r="M19" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:conditionalFormatting sqref="A5:M19">
-    <x:cfRule type="expression" dxfId="0" priority="1">
-      <x:formula>$M5=0</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:dataValidations count="6">
-    <x:dataValidation type="whole" operator="between" sqref="A5:A503">
-      <x:formula1>1</x:formula1>
-      <x:formula2>2147483647</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="D5:D503">
-      <x:formula1>0</x:formula1>
-      <x:formula2>10000</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="E5:E503">
-      <x:formula1>"player,weapon,tool"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="F5:F503">
-      <x:formula1>"numeric,mechanic"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="G5:G503">
-      <x:formula1>"passive,once,death"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="M5:M503">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-  </x:dataValidations>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76278d5528674b30"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="42" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="21" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="21" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="21" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="64" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="24" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="24" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="24" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="18" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="115" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="7" t="str">
+        <v>技能ID</v>
+      </c>
+      <c r="B1" s="7" t="str">
+        <v>技能名称</v>
+      </c>
+      <c r="C1" s="7" t="str">
+        <v>技能说明</v>
+      </c>
+      <c r="D1" s="7" t="str">
+        <v>消耗技能点</v>
+      </c>
+      <c r="E1" s="7" t="str">
+        <v>作用对象</v>
+      </c>
+      <c r="F1" s="7" t="str">
+        <v>效果类别</v>
+      </c>
+      <c r="G1" s="7" t="str">
+        <v>生命周期</v>
+      </c>
+      <c r="H1" s="7" t="str">
+        <v>效果展示说明</v>
+      </c>
+      <c r="I1" s="7" t="str">
+        <v>技能图标</v>
+      </c>
+      <c r="J1" s="7" t="str">
+        <v>动画资源</v>
+      </c>
+      <c r="K1" s="7" t="str">
+        <v>特效资源</v>
+      </c>
+      <c r="L1" s="7" t="str">
+        <v>音效资源</v>
+      </c>
+      <c r="M1" s="7" t="str">
+        <v>是否启用</v>
+      </c>
+      <c r="O1" s="28" t="str">
+        <v>技能配置说明</v>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="7" t="str">
+        <v>int32</v>
+      </c>
+      <c r="B2" s="7" t="str">
+        <v>string</v>
+      </c>
+      <c r="C2" s="7" t="str">
+        <v>string</v>
+      </c>
+      <c r="D2" s="7" t="str">
+        <v>int32</v>
+      </c>
+      <c r="E2" s="7" t="str">
+        <v>string</v>
+      </c>
+      <c r="F2" s="7" t="str">
+        <v>string</v>
+      </c>
+      <c r="G2" s="7" t="str">
+        <v>string</v>
+      </c>
+      <c r="H2" s="7" t="str">
+        <v>string</v>
+      </c>
+      <c r="I2" s="7" t="str">
+        <v>string</v>
+      </c>
+      <c r="J2" s="7" t="str">
+        <v>string</v>
+      </c>
+      <c r="K2" s="7" t="str">
+        <v>string</v>
+      </c>
+      <c r="L2" s="7" t="str">
+        <v>string</v>
+      </c>
+      <c r="M2" s="7" t="str">
+        <v>int32</v>
+      </c>
+      <c r="O2" s="26" t="str">
+        <v>来源：技能表完整配置方案.md（2026-10-03）</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="7" t="str">
+        <v>SkillIdx</v>
+      </c>
+      <c r="B3" s="7" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C3" s="7" t="str">
+        <v>Desc</v>
+      </c>
+      <c r="D3" s="7" t="str">
+        <v>Cost</v>
+      </c>
+      <c r="E3" s="7" t="str">
+        <v>Target</v>
+      </c>
+      <c r="F3" s="7" t="str">
+        <v>Category</v>
+      </c>
+      <c r="G3" s="7" t="str">
+        <v>Lifetime</v>
+      </c>
+      <c r="H3" s="7" t="str">
+        <v>EffectDesc</v>
+      </c>
+      <c r="I3" s="7" t="str">
+        <v>IconId</v>
+      </c>
+      <c r="J3" s="7" t="str">
+        <v>AnimId</v>
+      </c>
+      <c r="K3" s="7" t="str">
+        <v>EffectId</v>
+      </c>
+      <c r="L3" s="7" t="str">
+        <v>SoundId</v>
+      </c>
+      <c r="M3" s="7" t="str">
+        <v>Enabled</v>
+      </c>
+      <c r="O3" s="26"/>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="str">
+        <v>server/client/key</v>
+      </c>
+      <c r="B4" s="7" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="C4" s="7" t="str">
+        <v>client</v>
+      </c>
+      <c r="D4" s="7" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="E4" s="7" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="F4" s="7" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="G4" s="7" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="H4" s="7" t="str">
+        <v>client</v>
+      </c>
+      <c r="I4" s="7" t="str">
+        <v>client</v>
+      </c>
+      <c r="J4" s="7" t="str">
+        <v>client</v>
+      </c>
+      <c r="K4" s="7" t="str">
+        <v>client</v>
+      </c>
+      <c r="L4" s="7" t="str">
+        <v>client</v>
+      </c>
+      <c r="M4" s="7" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="O4" s="26"/>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="14" t="str">
+        <v>死灵法师</v>
+      </c>
+      <c r="C5" s="21" t="str">
+        <v>可在对局中复活一次</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="14" t="str">
+        <v>player</v>
+      </c>
+      <c r="F5" s="14" t="str">
+        <v>mechanic</v>
+      </c>
+      <c r="G5" s="14" t="str">
+        <v>once</v>
+      </c>
+      <c r="H5" s="21" t="str">
+        <v>成功复活恢复25点生命和40点体力，本局只能使用一次</v>
+      </c>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="26" t="str">
+        <v>15项技能完整保留，技能ID和技能点成本不变。</v>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="18" t="str">
+        <v>重振旗鼓</v>
+      </c>
+      <c r="C6" s="22" t="str">
+        <v>复活后将血量恢复至上限</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="18" t="str">
+        <v>player</v>
+      </c>
+      <c r="F6" s="18" t="str">
+        <v>mechanic</v>
+      </c>
+      <c r="G6" s="18" t="str">
+        <v>death</v>
+      </c>
+      <c r="H6" s="22" t="str">
+        <v>成功复活时恢复至最大生命，复活后移除本技能</v>
+      </c>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="26" t="str">
+        <v>技能3、6、14、15尚待扩展，Enabled=0；其余11项按方案填1。</v>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="14" t="str">
+        <v>精力充沛</v>
+      </c>
+      <c r="C7" s="21" t="str">
+        <v>降低奔跑时体力消耗</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="14" t="str">
+        <v>player</v>
+      </c>
+      <c r="F7" s="14" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="G7" s="14" t="str">
+        <v>passive</v>
+      </c>
+      <c r="H7" s="21" t="str">
+        <v>奔跑体力消耗降低30%</v>
+      </c>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="26" t="str">
+        <v>全部数值按方案初值填写。1表示候选调试启用，仍须通过运行能力校验。</v>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="18" t="str">
+        <v>军需官</v>
+      </c>
+      <c r="C8" s="22" t="str">
+        <v>提升角色负重能力</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="18" t="str">
+        <v>player</v>
+      </c>
+      <c r="F8" s="18" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="G8" s="18" t="str">
+        <v>passive</v>
+      </c>
+      <c r="H8" s="22" t="str">
+        <v>枪械配装负重上限增加1点</v>
+      </c>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="26" t="str">
+        <v>图标、动画、特效、音效尚无真实资源ID，空值表示未提供。</v>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="14" t="str">
+        <v>灵缇</v>
+      </c>
+      <c r="C9" s="21" t="str">
+        <v>提升一定奔跑速度</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="14" t="str">
+        <v>player</v>
+      </c>
+      <c r="F9" s="14" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="G9" s="14" t="str">
+        <v>passive</v>
+      </c>
+      <c r="H9" s="21" t="str">
+        <v>奔跑速度增加20%</v>
+      </c>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="26" t="str">
+        <v>AttributeId与Enabled由服务端解析校验；禁用技能不进入运行内容。</v>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="18" t="str">
+        <v>猫步</v>
+      </c>
+      <c r="C10" s="22" t="str">
+        <v>降低角色行动时发出的声音</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="18" t="str">
+        <v>player</v>
+      </c>
+      <c r="F10" s="18" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="G10" s="18" t="str">
+        <v>passive</v>
+      </c>
+      <c r="H10" s="22" t="str">
+        <v>地面行走、奔跑和匍匐的行动声传播半径降低50%</v>
+      </c>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="26" t="str">
+        <v>货运骡子增加每种适用工具的携带次数上限，不自动补发数量或库存。</v>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="14" t="str">
+        <v>枪斗术</v>
+      </c>
+      <c r="C11" s="21" t="str">
+        <v>增加枪械近战伤害</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="14" t="str">
+        <v>weapon</v>
+      </c>
+      <c r="F11" s="14" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="G11" s="14" t="str">
+        <v>passive</v>
+      </c>
+      <c r="H11" s="21" t="str">
+        <v>枪械近战伤害增加50%</v>
+      </c>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="26" t="str">
+        <v>技能10按枪械射击间隔shot_ticks配置，不修改瞄准精度或切枪速度。</v>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="18" t="str">
+        <v>弹药大师</v>
+      </c>
+      <c r="C12" s="22" t="str">
+        <v>提升枪械初始备弹</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="18" t="str">
+        <v>weapon</v>
+      </c>
+      <c r="F12" s="18" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="G12" s="18" t="str">
+        <v>passive</v>
+      </c>
+      <c r="H12" s="22" t="str">
+        <v>开局时枪械初始备弹翻倍，不增加弹匣容量</v>
+      </c>
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="26" t="str">
+        <v>once/death均在成功复活提交时消费，失败请求不消费。</v>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="14" t="str">
+        <v>手速超群</v>
+      </c>
+      <c r="C13" s="21" t="str">
+        <v>减少换弹时间</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="14" t="str">
+        <v>weapon</v>
+      </c>
+      <c r="F13" s="14" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="G13" s="14" t="str">
+        <v>passive</v>
+      </c>
+      <c r="H13" s="21" t="str">
+        <v>枪械每轮装填时间减少25%</v>
+      </c>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="26" t="str">
+        <v>技能效果在技能效果表逐项维护，EffectDesc仅用于展示。</v>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="18" t="str">
+        <v>稳定瞄准</v>
+      </c>
+      <c r="C14" s="22" t="str">
+        <v>减少武器轮转时间，本版指射击间隔</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="18" t="str">
+        <v>weapon</v>
+      </c>
+      <c r="F14" s="18" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="G14" s="18" t="str">
+        <v>passive</v>
+      </c>
+      <c r="H14" s="22" t="str">
+        <v>枪械射击间隔减少20%</v>
+      </c>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="14" t="str">
+        <v>妙手回春</v>
+      </c>
+      <c r="C15" s="21" t="str">
+        <v>医疗包的使用时长减半</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14" t="str">
+        <v>tool</v>
+      </c>
+      <c r="F15" s="14" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="G15" s="14" t="str">
+        <v>passive</v>
+      </c>
+      <c r="H15" s="21" t="str">
+        <v>医疗包使用时长减少50%</v>
+      </c>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="18" t="str">
+        <v>灵丹妙药</v>
+      </c>
+      <c r="C16" s="22" t="str">
+        <v>医疗包的治疗效果翻倍</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="18" t="str">
+        <v>tool</v>
+      </c>
+      <c r="F16" s="18" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="G16" s="18" t="str">
+        <v>passive</v>
+      </c>
+      <c r="H16" s="22" t="str">
+        <v>医疗包治疗量翻倍，实际生命不超过最大生命</v>
+      </c>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="14" t="str">
+        <v>投球好手</v>
+      </c>
+      <c r="C17" s="21" t="str">
+        <v>增加投掷物投掷距离</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="14" t="str">
+        <v>tool</v>
+      </c>
+      <c r="F17" s="14" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="G17" s="14" t="str">
+        <v>passive</v>
+      </c>
+      <c r="H17" s="21" t="str">
+        <v>当前已实现的炸药最大投掷距离增加50%</v>
+      </c>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="18" t="str">
+        <v>开箱大师</v>
+      </c>
+      <c r="C18" s="22" t="str">
+        <v>互动道具箱时可以额外获得一个道具</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="18" t="str">
+        <v>player</v>
+      </c>
+      <c r="F18" s="18" t="str">
+        <v>mechanic</v>
+      </c>
+      <c r="G18" s="18" t="str">
+        <v>passive</v>
+      </c>
+      <c r="H18" s="22" t="str">
+        <v>成功打开适用道具箱时，额外取得同一箱子奖励来源中的1个道具</v>
+      </c>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="14" t="str">
+        <v>货运骡子</v>
+      </c>
+      <c r="C19" s="21" t="str">
+        <v>非消耗品道具额外增加携带量</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="14" t="str">
+        <v>tool</v>
+      </c>
+      <c r="F19" s="14" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="G19" s="14" t="str">
+        <v>passive</v>
+      </c>
+      <c r="H19" s="21" t="str">
+        <v>每种适用非消耗品工具的携带次数上限增加1，不自动补发数量</v>
+      </c>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A5:M19">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$M5=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="6">
+    <dataValidation type="whole" operator="between" sqref="A5:A503">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" sqref="D5:D503">
+      <formula1>0</formula1>
+      <formula2>10000</formula2>
+    </dataValidation>
+    <dataValidation type="list" sqref="E5:E503">
+      <formula1>"player,weapon,tool"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="F5:F503">
+      <formula1>"numeric,mechanic"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="G5:G503">
+      <formula1>"passive,once,death"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" sqref="M5:M503">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="R76278d5528674b30"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
